--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\U11_Coach_V1.125_PWA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF5F1FA-B066-4C71-A972-EDDF1FE2343F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9F59D6-902E-4CA8-8D10-92359B74CFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5805" yWindow="1875" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="46">
   <si>
     <t>Spieler</t>
   </si>
@@ -153,7 +153,13 @@
     <t>13</t>
   </si>
   <si>
-    <t>1 + 9</t>
+    <t>Offene Trikotnummern</t>
+  </si>
+  <si>
+    <t>8, 14</t>
+  </si>
+  <si>
+    <t>1+9</t>
   </si>
 </sst>
 </file>
@@ -252,7 +258,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -318,17 +331,17 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -343,7 +356,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -358,26 +371,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +621,7 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -658,7 +673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -684,7 +699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -710,7 +725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -736,7 +751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -762,7 +777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -788,7 +803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -799,7 +814,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>8</v>
@@ -808,13 +823,13 @@
         <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -840,7 +855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -848,13 +863,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
@@ -866,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -874,25 +889,25 @@
         <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="1">
-        <v>2</v>
-      </c>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
       <c r="H11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -900,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
@@ -918,7 +933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -944,7 +959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -955,7 +970,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -964,13 +979,13 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -996,7 +1011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1022,7 +1037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1048,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1100,7 +1115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
   </sheetData>
@@ -1118,20 +1133,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1408,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1416,16 +1431,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1480,7 +1495,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1563,10 +1578,18 @@
       </c>
       <c r="B22" s="15"/>
     </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9F59D6-902E-4CA8-8D10-92359B74CFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A97709-6761-4249-9801-77CFDFF0FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
   <si>
     <t>Spieler</t>
   </si>
@@ -156,10 +156,13 @@
     <t>Offene Trikotnummern</t>
   </si>
   <si>
-    <t>8, 14</t>
-  </si>
-  <si>
     <t>1+9</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -381,18 +384,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,7 +1139,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="18"/>
@@ -1141,7 +1147,7 @@
       <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="18"/>
@@ -1431,13 +1437,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="18"/>
@@ -1495,7 +1501,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1534,19 +1540,22 @@
       <c r="A15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="15" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="15"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="15"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
@@ -1561,30 +1570,22 @@
       <c r="B19" s="15"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="A20" s="14"/>
       <c r="B20" s="15"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>24</v>
-      </c>
+      <c r="A21" s="14"/>
       <c r="B21" s="15"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="A22" s="14"/>
       <c r="B22" s="15"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>44</v>
-      </c>
+      <c r="B29" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A97709-6761-4249-9801-77CFDFF0FFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD20BA-BA52-47CB-BC62-9BB57103F828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="48">
   <si>
     <t>Spieler</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>8</t>
+  </si>
+  <si>
+    <t>Kenan</t>
   </si>
 </sst>
 </file>
@@ -384,21 +387,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,20 +1142,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1437,16 +1440,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1553,8 +1556,8 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>19</v>
+      <c r="A17" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1570,7 +1573,9 @@
       <c r="B19" s="15"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="B20" s="15"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BD20BA-BA52-47CB-BC62-9BB57103F828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BEE007-8AAB-4F3C-B2E6-75CC9089C7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="50">
   <si>
     <t>Spieler</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>Kenan</t>
+  </si>
+  <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>Florian</t>
   </si>
 </sst>
 </file>
@@ -339,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -401,6 +407,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -421,7 +430,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D22" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D25" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Priorität 1"/>
@@ -627,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1125,7 +1134,56 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="23">
+        <v>2</v>
+      </c>
+      <c r="C20" s="23">
+        <v>3</v>
+      </c>
+      <c r="D20" s="23">
+        <v>4</v>
+      </c>
+      <c r="E20" s="23">
+        <v>2</v>
+      </c>
+      <c r="F20" s="23">
+        <v>2</v>
+      </c>
+      <c r="G20" s="23">
+        <v>3</v>
+      </c>
+      <c r="H20" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="23">
+        <v>1</v>
+      </c>
+      <c r="C21" s="23">
+        <v>1</v>
+      </c>
+      <c r="D21" s="23">
+        <v>1</v>
+      </c>
+      <c r="E21" s="23">
+        <v>1</v>
+      </c>
+      <c r="F21" s="23">
+        <v>1</v>
+      </c>
+      <c r="G21" s="23">
+        <v>1</v>
+      </c>
+      <c r="H21" s="23">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1134,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1413,13 +1471,23 @@
       </c>
       <c r="D22" s="12"/>
     </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B5:D22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B5:D25" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Torwart,Abwehr,Mittelfeld,Sturm,Spielmacher"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BEE007-8AAB-4F3C-B2E6-75CC9089C7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9EE33-7E84-4324-9E52-EFED2C41F48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,21 +396,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -852,10 +852,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -867,10 +867,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1137,52 +1137,52 @@
       <c r="A20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="23">
-        <v>2</v>
-      </c>
-      <c r="C20" s="23">
-        <v>3</v>
-      </c>
-      <c r="D20" s="23">
-        <v>4</v>
-      </c>
-      <c r="E20" s="23">
-        <v>2</v>
-      </c>
-      <c r="F20" s="23">
-        <v>2</v>
-      </c>
-      <c r="G20" s="23">
-        <v>3</v>
-      </c>
-      <c r="H20" s="23">
+      <c r="B20" s="18">
+        <v>2</v>
+      </c>
+      <c r="C20" s="18">
+        <v>4</v>
+      </c>
+      <c r="D20" s="18">
+        <v>4</v>
+      </c>
+      <c r="E20" s="18">
+        <v>2</v>
+      </c>
+      <c r="F20" s="18">
+        <v>2</v>
+      </c>
+      <c r="G20" s="18">
+        <v>3</v>
+      </c>
+      <c r="H20" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="23">
-        <v>1</v>
-      </c>
-      <c r="C21" s="23">
-        <v>1</v>
-      </c>
-      <c r="D21" s="23">
-        <v>1</v>
-      </c>
-      <c r="E21" s="23">
-        <v>1</v>
-      </c>
-      <c r="F21" s="23">
-        <v>1</v>
-      </c>
-      <c r="G21" s="23">
-        <v>1</v>
-      </c>
-      <c r="H21" s="23">
-        <v>1</v>
+      <c r="B21" s="18">
+        <v>1</v>
+      </c>
+      <c r="C21" s="18">
+        <v>3</v>
+      </c>
+      <c r="D21" s="18">
+        <v>2</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3</v>
+      </c>
+      <c r="F21" s="18">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18">
+        <v>3</v>
+      </c>
+      <c r="H21" s="18">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1200,20 +1200,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1508,16 +1508,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="20"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9EE33-7E84-4324-9E52-EFED2C41F48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B2E44-9662-495B-A67D-40D5A91783D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,11 +183,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
     </font>
     <font>
       <b/>
@@ -230,6 +225,13 @@
       <sz val="11"/>
       <color rgb="FF334155"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -347,16 +349,13 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -365,7 +364,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -374,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -383,7 +382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -392,24 +391,27 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -881,13 +883,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
@@ -1134,54 +1136,54 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="18">
-        <v>2</v>
-      </c>
-      <c r="C20" s="18">
-        <v>4</v>
-      </c>
-      <c r="D20" s="18">
-        <v>4</v>
-      </c>
-      <c r="E20" s="18">
-        <v>2</v>
-      </c>
-      <c r="F20" s="18">
-        <v>2</v>
-      </c>
-      <c r="G20" s="18">
-        <v>3</v>
-      </c>
-      <c r="H20" s="18">
+      <c r="B20" s="17">
+        <v>2</v>
+      </c>
+      <c r="C20" s="17">
+        <v>4</v>
+      </c>
+      <c r="D20" s="17">
+        <v>4</v>
+      </c>
+      <c r="E20" s="17">
+        <v>2</v>
+      </c>
+      <c r="F20" s="17">
+        <v>2</v>
+      </c>
+      <c r="G20" s="17">
+        <v>3</v>
+      </c>
+      <c r="H20" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="18">
-        <v>1</v>
-      </c>
-      <c r="C21" s="18">
-        <v>3</v>
-      </c>
-      <c r="D21" s="18">
-        <v>2</v>
-      </c>
-      <c r="E21" s="18">
-        <v>3</v>
-      </c>
-      <c r="F21" s="18">
-        <v>1</v>
-      </c>
-      <c r="G21" s="18">
-        <v>3</v>
-      </c>
-      <c r="H21" s="18">
+      <c r="B21" s="17">
+        <v>1</v>
+      </c>
+      <c r="C21" s="17">
+        <v>3</v>
+      </c>
+      <c r="D21" s="17">
+        <v>2</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3</v>
+      </c>
+      <c r="F21" s="17">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17">
+        <v>3</v>
+      </c>
+      <c r="H21" s="17">
         <v>3</v>
       </c>
     </row>
@@ -1200,276 +1202,276 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="B9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="B11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="B13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="B14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="B15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="B16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="B17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="9"/>
+      <c r="B18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="9"/>
+      <c r="B19" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="9"/>
+      <c r="B20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="9"/>
+      <c r="B21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="12"/>
+      <c r="B22" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1508,157 +1510,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="14"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="15"/>
+      <c r="B19" s="14"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="14"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B2E44-9662-495B-A67D-40D5A91783D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7B3DFE-D8EF-439B-B365-3BF8AD4E8C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,6 +398,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -409,9 +412,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,13 +678,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -1136,7 +1136,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B20" s="17">
@@ -1149,13 +1149,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="17">
         <v>3</v>
@@ -1202,20 +1202,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1510,16 +1510,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="20"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7B3DFE-D8EF-439B-B365-3BF8AD4E8C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E963E5-02F0-4F59-B14A-077DBFA999CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -727,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
         <v>9</v>
@@ -736,13 +736,13 @@
         <v>6</v>
       </c>
       <c r="F4" s="1">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1">
         <v>6</v>
-      </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -808,7 +808,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1">
         <v>8</v>
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
         <v>7</v>
@@ -857,7 +857,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -866,7 +866,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E963E5-02F0-4F59-B14A-077DBFA999CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EE9F5C-9107-4B71-9D9D-8A1731CEA969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1348,10 +1348,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\U11_Coach_V1.198_PWA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EE9F5C-9107-4B71-9D9D-8A1731CEA969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07858B5-BC7A-4B25-9694-0E920B83815B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
     <sheet name="Positionspriorität" sheetId="2" r:id="rId2"/>
     <sheet name="Trikotnummern" sheetId="3" r:id="rId3"/>
+    <sheet name="Spielerkader" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="55">
   <si>
     <t>Spieler</t>
   </si>
@@ -141,6 +142,9 @@
     <t>3</t>
   </si>
   <si>
+    <t>1 / 9</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -153,32 +157,44 @@
     <t>13</t>
   </si>
   <si>
-    <t>Offene Trikotnummern</t>
-  </si>
-  <si>
-    <t>1+9</t>
+    <t>Spielerkader</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>Nein</t>
+  </si>
+  <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>Florian</t>
+  </si>
+  <si>
+    <t>Hinweis</t>
+  </si>
+  <si>
+    <t>Ja = im Spielerkader sichtbar, Nein = nicht im Spielerkader sichtbar.</t>
+  </si>
+  <si>
+    <t>Pflege</t>
+  </si>
+  <si>
+    <t>Diese Tabelle steuert ausschließlich die Seite „Spielerkader“ in der PWA.</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>Kenan</t>
-  </si>
-  <si>
-    <t>Jonas</t>
-  </si>
-  <si>
-    <t>Florian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +243,11 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -234,7 +255,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,6 +290,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5122F"/>
       </patternFill>
     </fill>
   </fills>
@@ -344,15 +370,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -367,7 +395,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -382,41 +410,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{D78C052E-F79A-417D-B71C-EF3D37759E22}"/>
+    <cellStyle name="Standard 3" xfId="2" xr:uid="{6051B7CB-5C5C-4E99-82FC-A68CA8B1E8E6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -432,12 +469,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D25" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D22" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Priorität 1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priorität 2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priorität 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B21" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Spielerkader"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -641,7 +688,7 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -678,13 +725,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
       </c>
       <c r="F2" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -693,7 +740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -719,7 +766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -727,7 +774,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
         <v>9</v>
@@ -736,16 +783,16 @@
         <v>6</v>
       </c>
       <c r="F4" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -771,7 +818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -797,7 +844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -808,7 +855,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1">
         <v>8</v>
@@ -823,7 +870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -834,30 +881,30 @@
         <v>7</v>
       </c>
       <c r="D8" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1">
         <v>8</v>
       </c>
       <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -866,16 +913,16 @@
         <v>4</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -883,13 +930,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
@@ -901,7 +948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -909,25 +956,25 @@
         <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="E11" s="1">
-        <v>5</v>
-      </c>
       <c r="F11" s="1">
         <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -935,7 +982,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
@@ -953,7 +1000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -979,7 +1026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -990,7 +1037,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
@@ -999,13 +1046,13 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1031,7 +1078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1057,7 +1104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1083,7 +1130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -1109,7 +1156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1135,55 +1182,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="23">
+        <v>2</v>
+      </c>
+      <c r="C20" s="23">
+        <v>4</v>
+      </c>
+      <c r="D20" s="23">
+        <v>4</v>
+      </c>
+      <c r="E20" s="23">
+        <v>3</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1</v>
+      </c>
+      <c r="G20" s="23">
+        <v>4</v>
+      </c>
+      <c r="H20" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="17">
-        <v>2</v>
-      </c>
-      <c r="C20" s="17">
-        <v>4</v>
-      </c>
-      <c r="D20" s="17">
-        <v>4</v>
-      </c>
-      <c r="E20" s="17">
-        <v>3</v>
-      </c>
-      <c r="F20" s="17">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17">
-        <v>4</v>
-      </c>
-      <c r="H20" s="17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="17">
-        <v>1</v>
-      </c>
-      <c r="C21" s="17">
-        <v>3</v>
-      </c>
-      <c r="D21" s="17">
-        <v>2</v>
-      </c>
-      <c r="E21" s="17">
-        <v>3</v>
-      </c>
-      <c r="F21" s="17">
-        <v>1</v>
-      </c>
-      <c r="G21" s="17">
-        <v>3</v>
-      </c>
-      <c r="H21" s="17">
+      <c r="B21" s="23">
+        <v>1</v>
+      </c>
+      <c r="C21" s="23">
+        <v>3</v>
+      </c>
+      <c r="D21" s="23">
+        <v>2</v>
+      </c>
+      <c r="E21" s="23">
+        <v>3</v>
+      </c>
+      <c r="F21" s="23">
+        <v>1</v>
+      </c>
+      <c r="G21" s="23">
+        <v>3</v>
+      </c>
+      <c r="H21" s="23">
         <v>3</v>
       </c>
     </row>
@@ -1194,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1205,12 +1252,12 @@
       <c r="A1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="20"/>
@@ -1348,10 +1395,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>
@@ -1472,16 +1519,6 @@
         <v>4</v>
       </c>
       <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1489,7 +1526,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B5:D25" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B5:D22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Torwart,Abwehr,Mittelfeld,Sturm,Spielmacher"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1502,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1510,16 +1547,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="22"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -1574,7 +1611,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1582,7 +1619,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1590,7 +1627,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1598,7 +1635,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1606,7 +1643,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1614,20 +1651,21 @@
         <v>18</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="14"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>47</v>
+      <c r="B17" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1644,29 +1682,247 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="14"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="14"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="B22" s="14"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="15"/>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B2:B21" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>"Ja,Nein"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\U11_Coach_V1.198_PWA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07858B5-BC7A-4B25-9694-0E920B83815B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585CB93E-EB18-46E7-8E9C-FAA5965A3B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -431,6 +431,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -442,12 +448,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -904,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -913,10 +913,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1">
         <v>8</v>
@@ -930,19 +930,19 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
       </c>
       <c r="F10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="1">
         <v>7</v>
@@ -1183,54 +1183,54 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="23">
-        <v>2</v>
-      </c>
-      <c r="C20" s="23">
-        <v>4</v>
-      </c>
-      <c r="D20" s="23">
-        <v>4</v>
-      </c>
-      <c r="E20" s="23">
-        <v>3</v>
-      </c>
-      <c r="F20" s="23">
-        <v>1</v>
-      </c>
-      <c r="G20" s="23">
-        <v>4</v>
-      </c>
-      <c r="H20" s="23">
+      <c r="B20" s="19">
+        <v>2</v>
+      </c>
+      <c r="C20" s="19">
+        <v>4</v>
+      </c>
+      <c r="D20" s="19">
+        <v>4</v>
+      </c>
+      <c r="E20" s="19">
+        <v>3</v>
+      </c>
+      <c r="F20" s="19">
+        <v>1</v>
+      </c>
+      <c r="G20" s="19">
+        <v>4</v>
+      </c>
+      <c r="H20" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="23">
-        <v>1</v>
-      </c>
-      <c r="C21" s="23">
-        <v>3</v>
-      </c>
-      <c r="D21" s="23">
-        <v>2</v>
-      </c>
-      <c r="E21" s="23">
-        <v>3</v>
-      </c>
-      <c r="F21" s="23">
-        <v>1</v>
-      </c>
-      <c r="G21" s="23">
-        <v>3</v>
-      </c>
-      <c r="H21" s="23">
+      <c r="B21" s="19">
+        <v>1</v>
+      </c>
+      <c r="C21" s="19">
+        <v>3</v>
+      </c>
+      <c r="D21" s="19">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>3</v>
+      </c>
+      <c r="F21" s="19">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19">
+        <v>3</v>
+      </c>
+      <c r="H21" s="19">
         <v>3</v>
       </c>
     </row>
@@ -1249,20 +1249,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1547,16 +1547,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="24"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585CB93E-EB18-46E7-8E9C-FAA5965A3B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93915BD-6D96-495E-8A85-656EAAF4E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,7 +757,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
         <v>9</v>
@@ -1216,19 +1216,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" s="19">
         <v>1</v>
       </c>
       <c r="G21" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H21" s="19">
         <v>3</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93915BD-6D96-495E-8A85-656EAAF4E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473855C5-C2B4-442F-B8F4-4B0FF9E9C4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="54">
   <si>
     <t>Spieler</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>Ali</t>
-  </si>
-  <si>
-    <t>Johannes Wiedmuth</t>
   </si>
   <si>
     <t>Johannes Suppmair</t>
@@ -469,7 +466,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D22" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D21" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Priorität 1"/>
@@ -481,7 +478,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B20" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Spielerkader"/>
@@ -685,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
@@ -1104,7 +1101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1112,25 +1109,25 @@
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -1138,10 +1135,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -1153,84 +1150,58 @@
         <v>2</v>
       </c>
       <c r="H18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="A19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="19">
+        <v>2</v>
+      </c>
+      <c r="C19" s="19">
+        <v>4</v>
+      </c>
+      <c r="D19" s="19">
+        <v>4</v>
+      </c>
+      <c r="E19" s="19">
+        <v>3</v>
+      </c>
+      <c r="F19" s="19">
         <v>1</v>
       </c>
-      <c r="C19" s="1">
-        <v>4</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3</v>
-      </c>
-      <c r="E19" s="1">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="G19" s="19">
+        <v>4</v>
+      </c>
+      <c r="H19" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="19">
         <v>1</v>
       </c>
-      <c r="G19" s="1">
-        <v>2</v>
-      </c>
-      <c r="H19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="19">
-        <v>2</v>
-      </c>
       <c r="C20" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="19">
         <v>1</v>
       </c>
       <c r="G20" s="19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="19">
-        <v>1</v>
-      </c>
-      <c r="C21" s="19">
-        <v>5</v>
-      </c>
-      <c r="D21" s="19">
-        <v>3</v>
-      </c>
-      <c r="E21" s="19">
-        <v>2</v>
-      </c>
-      <c r="F21" s="19">
-        <v>1</v>
-      </c>
-      <c r="G21" s="19">
-        <v>8</v>
-      </c>
-      <c r="H21" s="19">
         <v>3</v>
       </c>
     </row>
@@ -1241,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1250,7 +1221,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1258,7 +1229,7 @@
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1269,13 +1240,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,33 +1463,21 @@
         <v>2</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="11"/>
+      <c r="B21" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1526,7 +1485,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B5:D22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B5:D21" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Torwart,Abwehr,Mittelfeld,Sturm,Spielmacher"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1539,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1548,13 +1507,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="24"/>
     </row>
@@ -1563,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1571,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1579,7 +1538,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1587,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1595,7 +1554,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1603,7 +1562,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1611,7 +1570,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1619,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1627,7 +1586,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1635,7 +1594,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1643,7 +1602,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1651,7 +1610,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1665,7 +1624,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1694,18 +1653,12 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="14"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1731,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1739,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1747,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1755,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1763,7 +1716,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1771,7 +1724,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1779,7 +1732,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1787,7 +1740,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1795,7 +1748,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1803,7 +1756,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1811,7 +1764,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1819,7 +1772,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1827,7 +1780,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1835,7 +1788,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1843,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1851,31 +1804,31 @@
         <v>22</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1883,40 +1836,32 @@
         <v>47</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+    </row>
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B21" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="B2:B20" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Ja,Nein"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473855C5-C2B4-442F-B8F4-4B0FF9E9C4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C2AB55-284F-4E61-AE17-E709E874DD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -1260,7 +1260,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1285,10 +1285,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1296,10 +1296,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>3</v>
@@ -1366,10 +1366,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C2AB55-284F-4E61-AE17-E709E874DD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717A5389-61BD-4554-87D4-65742B795D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -452,7 +452,188 @@
     <cellStyle name="Standard 2" xfId="1" xr:uid="{D78C052E-F79A-417D-B71C-EF3D37759E22}"/>
     <cellStyle name="Standard 3" xfId="2" xr:uid="{6051B7CB-5C5C-4E99-82FC-A68CA8B1E8E6}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -466,6 +647,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B0522708-B711-496B-8563-235014E8DB00}" name="Tabelle1" displayName="Tabelle1" ref="A1:H20" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3" dataCellStyle="Standard 3">
+  <autoFilter ref="A1:H20" xr:uid="{B0522708-B711-496B-8563-235014E8DB00}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{2B8843DC-F700-49D9-99C4-9BA7F9836F9A}" name="Spieler" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{173F1290-84DD-4B1C-864C-A09F799D218B}" name="Torwart" dataDxfId="0" dataCellStyle="Standard 3"/>
+    <tableColumn id="3" xr3:uid="{05635FD0-3621-4C46-A81E-44FEFA3A7B2F}" name="Abwehr" dataDxfId="9" dataCellStyle="Standard 3"/>
+    <tableColumn id="4" xr3:uid="{B6B90E09-590C-4961-844A-9E957A911E30}" name="Mittelfeld" dataDxfId="8" dataCellStyle="Standard 3"/>
+    <tableColumn id="5" xr3:uid="{B5CAA08C-2B7E-4F44-A58A-FC9D963EF079}" name="Sturm" dataDxfId="7" dataCellStyle="Standard 3"/>
+    <tableColumn id="6" xr3:uid="{619E13C9-DF25-40D1-970F-7398CFEB0036}" name="Spielmacher" dataDxfId="6" dataCellStyle="Standard 3"/>
+    <tableColumn id="7" xr3:uid="{FA8BC8BB-4566-496D-B4C1-6FB1E75968C7}" name="Ausdauer" dataDxfId="5" dataCellStyle="Standard 3"/>
+    <tableColumn id="8" xr3:uid="{8D5E650C-45AC-49E4-B4DE-0FE211B65012}" name="Körper" dataDxfId="4" dataCellStyle="Standard 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D21" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
@@ -477,7 +675,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B20" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
@@ -684,6 +882,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1207,6 +1410,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717A5389-61BD-4554-87D4-65742B795D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52AF7FE-EFA2-4D42-876D-5AC744ED69CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,6 +100,12 @@
     <t>Tamino</t>
   </si>
   <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>Florian</t>
+  </si>
+  <si>
     <t>Positionspriorität – U11 Coach</t>
   </si>
   <si>
@@ -154,6 +160,12 @@
     <t>13</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>Spielerkader</t>
   </si>
   <si>
@@ -163,12 +175,6 @@
     <t>Nein</t>
   </si>
   <si>
-    <t>Jonas</t>
-  </si>
-  <si>
-    <t>Florian</t>
-  </si>
-  <si>
     <t>Hinweis</t>
   </si>
   <si>
@@ -179,12 +185,6 @@
   </si>
   <si>
     <t>Diese Tabelle steuert ausschließlich die Seite „Spielerkader“ in der PWA.</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
 </sst>
 </file>
@@ -252,7 +252,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +292,56 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5122F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE8E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6343A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB6266"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4A5A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE787C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF18E92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE31E24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE94B50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9D2D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7BCBD"/>
       </patternFill>
     </fill>
   </fills>
@@ -368,16 +418,16 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -392,7 +442,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -407,25 +457,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
@@ -434,204 +484,223 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="1" xr:uid="{D78C052E-F79A-417D-B71C-EF3D37759E22}"/>
-    <cellStyle name="Standard 3" xfId="2" xr:uid="{6051B7CB-5C5C-4E99-82FC-A68CA8B1E8E6}"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Standard 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Aptos"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,39 +716,39 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B0522708-B711-496B-8563-235014E8DB00}" name="Tabelle1" displayName="Tabelle1" ref="A1:H20" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3" dataCellStyle="Standard 3">
-  <autoFilter ref="A1:H20" xr:uid="{B0522708-B711-496B-8563-235014E8DB00}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:H20" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" dataCellStyle="Standard 3">
+  <autoFilter ref="A1:H20" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2B8843DC-F700-49D9-99C4-9BA7F9836F9A}" name="Spieler" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{173F1290-84DD-4B1C-864C-A09F799D218B}" name="Torwart" dataDxfId="0" dataCellStyle="Standard 3"/>
-    <tableColumn id="3" xr3:uid="{05635FD0-3621-4C46-A81E-44FEFA3A7B2F}" name="Abwehr" dataDxfId="9" dataCellStyle="Standard 3"/>
-    <tableColumn id="4" xr3:uid="{B6B90E09-590C-4961-844A-9E957A911E30}" name="Mittelfeld" dataDxfId="8" dataCellStyle="Standard 3"/>
-    <tableColumn id="5" xr3:uid="{B5CAA08C-2B7E-4F44-A58A-FC9D963EF079}" name="Sturm" dataDxfId="7" dataCellStyle="Standard 3"/>
-    <tableColumn id="6" xr3:uid="{619E13C9-DF25-40D1-970F-7398CFEB0036}" name="Spielmacher" dataDxfId="6" dataCellStyle="Standard 3"/>
-    <tableColumn id="7" xr3:uid="{FA8BC8BB-4566-496D-B4C1-6FB1E75968C7}" name="Ausdauer" dataDxfId="5" dataCellStyle="Standard 3"/>
-    <tableColumn id="8" xr3:uid="{8D5E650C-45AC-49E4-B4DE-0FE211B65012}" name="Körper" dataDxfId="4" dataCellStyle="Standard 3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Torwart" dataDxfId="6" dataCellStyle="Standard 3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Abwehr" dataDxfId="5" dataCellStyle="Standard 3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Mittelfeld" dataDxfId="4" dataCellStyle="Standard 3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Sturm" dataDxfId="3" dataCellStyle="Standard 3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Spielmacher" dataDxfId="2" dataCellStyle="Standard 3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ausdauer" dataDxfId="1" dataCellStyle="Standard 3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Körper" dataDxfId="0" dataCellStyle="Standard 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D21" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Priorität 1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priorität 2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priorität 3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Priorität 1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Priorität 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Priorität 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B20" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="SpielerkaderTable" displayName="SpielerkaderTable" ref="A1:B20" totalsRowShown="0">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Spielerkader"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Spieler"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Spielerkader"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -888,7 +957,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -914,501 +983,513 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="21">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="22">
         <v>9</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="23">
+        <v>6</v>
+      </c>
+      <c r="E2" s="24">
+        <v>4</v>
+      </c>
+      <c r="F2" s="23">
         <v>7</v>
       </c>
-      <c r="E2" s="1">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="G2" s="25">
         <v>6</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="25">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="22">
         <v>9</v>
       </c>
-      <c r="D3" s="1">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="27">
+        <v>9</v>
+      </c>
+      <c r="E3" s="23">
         <v>7</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="26">
         <v>5</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="22">
         <v>9</v>
       </c>
-      <c r="H3" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H3" s="27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="25">
         <v>6</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="28">
         <v>8</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="22">
         <v>9</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="25">
         <v>6</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="25">
         <v>6</v>
       </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="G4" s="27">
+        <v>9</v>
+      </c>
+      <c r="H4" s="23">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="29">
+        <v>2</v>
+      </c>
+      <c r="C5" s="23">
         <v>7</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="23">
         <v>7</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="23">
         <v>7</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="25">
         <v>6</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="28">
         <v>8</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="25">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="26">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="26">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="28">
         <v>8</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="28">
         <v>8</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="28">
         <v>8</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="26">
         <v>5</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="28">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="22">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="26">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="25">
         <v>6</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="28">
         <v>8</v>
       </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7" s="30">
+        <v>3</v>
+      </c>
+      <c r="G7" s="23">
         <v>7</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="26">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="23">
         <v>7</v>
       </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="24">
+        <v>4</v>
+      </c>
+      <c r="E8" s="28">
         <v>8</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="26">
         <v>5</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="25">
         <v>6</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="23">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="28">
         <v>8</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="23">
         <v>7</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="26">
         <v>5</v>
       </c>
-      <c r="E9" s="1">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="E9" s="24">
+        <v>4</v>
+      </c>
+      <c r="F9" s="29">
+        <v>2</v>
+      </c>
+      <c r="G9" s="24">
+        <v>4</v>
+      </c>
+      <c r="H9" s="28">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B10" s="30">
+        <v>3</v>
+      </c>
+      <c r="C10" s="23">
         <v>7</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="25">
         <v>6</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="26">
         <v>5</v>
       </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="F10" s="30">
+        <v>3</v>
+      </c>
+      <c r="G10" s="23">
         <v>7</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="23">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11" s="1">
-        <v>4</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="29">
+        <v>2</v>
+      </c>
+      <c r="C11" s="24">
+        <v>4</v>
+      </c>
+      <c r="D11" s="26">
         <v>5</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="25">
         <v>6</v>
       </c>
-      <c r="F11" s="1">
-        <v>2</v>
-      </c>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="F11" s="29">
+        <v>2</v>
+      </c>
+      <c r="G11" s="22">
+        <v>7</v>
+      </c>
+      <c r="H11" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="1">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="B12" s="24">
+        <v>4</v>
+      </c>
+      <c r="C12" s="25">
         <v>6</v>
       </c>
-      <c r="D12" s="1">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="24">
+        <v>4</v>
+      </c>
+      <c r="E12" s="26">
         <v>5</v>
       </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F12" s="29">
+        <v>2</v>
+      </c>
+      <c r="G12" s="26">
         <v>5</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="23">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="B13" s="29">
+        <v>2</v>
+      </c>
+      <c r="C13" s="24">
+        <v>4</v>
+      </c>
+      <c r="D13" s="26">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="25">
         <v>6</v>
       </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>4</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="F13" s="29">
+        <v>2</v>
+      </c>
+      <c r="G13" s="24">
+        <v>4</v>
+      </c>
+      <c r="H13" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1">
-        <v>3</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="B14" s="29">
+        <v>2</v>
+      </c>
+      <c r="C14" s="24">
+        <v>4</v>
+      </c>
+      <c r="D14" s="24">
+        <v>4</v>
+      </c>
+      <c r="E14" s="24">
+        <v>4</v>
+      </c>
+      <c r="F14" s="29">
+        <v>2</v>
+      </c>
+      <c r="G14" s="30">
+        <v>3</v>
+      </c>
+      <c r="H14" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="1">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3</v>
-      </c>
-      <c r="E15" s="1">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="B15" s="24">
+        <v>4</v>
+      </c>
+      <c r="C15" s="29">
+        <v>2</v>
+      </c>
+      <c r="D15" s="30">
+        <v>3</v>
+      </c>
+      <c r="E15" s="24">
+        <v>4</v>
+      </c>
+      <c r="F15" s="21">
         <v>1</v>
       </c>
-      <c r="G15" s="1">
-        <v>4</v>
-      </c>
-      <c r="H15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="24">
+        <v>4</v>
+      </c>
+      <c r="H15" s="29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="21">
         <v>1</v>
       </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="C16" s="29">
+        <v>2</v>
+      </c>
+      <c r="D16" s="29">
+        <v>2</v>
+      </c>
+      <c r="E16" s="29">
+        <v>2</v>
+      </c>
+      <c r="F16" s="21">
         <v>1</v>
       </c>
-      <c r="G16" s="1">
-        <v>3</v>
-      </c>
-      <c r="H16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="30">
+        <v>3</v>
+      </c>
+      <c r="H16" s="29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="21">
         <v>1</v>
       </c>
-      <c r="C17" s="1">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>3</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="C17" s="30">
+        <v>3</v>
+      </c>
+      <c r="D17" s="29">
+        <v>2</v>
+      </c>
+      <c r="E17" s="30">
+        <v>3</v>
+      </c>
+      <c r="F17" s="21">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
-        <v>2</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="29">
+        <v>2</v>
+      </c>
+      <c r="H17" s="30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="21">
         <v>1</v>
       </c>
-      <c r="C18" s="1">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
-        <v>3</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="C18" s="24">
+        <v>4</v>
+      </c>
+      <c r="D18" s="30">
+        <v>3</v>
+      </c>
+      <c r="E18" s="30">
+        <v>3</v>
+      </c>
+      <c r="F18" s="21">
         <v>1</v>
       </c>
-      <c r="G18" s="1">
-        <v>2</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="29">
+        <v>2</v>
+      </c>
+      <c r="H18" s="29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="19">
-        <v>2</v>
-      </c>
-      <c r="C19" s="19">
-        <v>4</v>
-      </c>
-      <c r="D19" s="19">
-        <v>4</v>
-      </c>
-      <c r="E19" s="19">
-        <v>3</v>
-      </c>
-      <c r="F19" s="19">
+        <v>25</v>
+      </c>
+      <c r="B19" s="31">
+        <v>2</v>
+      </c>
+      <c r="C19" s="32">
+        <v>4</v>
+      </c>
+      <c r="D19" s="32">
+        <v>4</v>
+      </c>
+      <c r="E19" s="33">
+        <v>3</v>
+      </c>
+      <c r="F19" s="34">
         <v>1</v>
       </c>
-      <c r="G19" s="19">
-        <v>4</v>
-      </c>
-      <c r="H19" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="32">
+        <v>4</v>
+      </c>
+      <c r="H19" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="19">
+        <v>26</v>
+      </c>
+      <c r="B20" s="34">
         <v>1</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="35">
         <v>5</v>
       </c>
-      <c r="D20" s="19">
-        <v>3</v>
-      </c>
-      <c r="E20" s="19">
-        <v>2</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="D20" s="33">
+        <v>3</v>
+      </c>
+      <c r="E20" s="31">
+        <v>2</v>
+      </c>
+      <c r="F20" s="34">
         <v>1</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="36">
         <v>8</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="33">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:H20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF4B7B7"/>
+        <color rgb="FFE31E24"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1426,33 +1507,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="A1" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="A2" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,24 +1792,24 @@
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="23"/>
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="38"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="24"/>
+      <c r="A2" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="38"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1736,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1744,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1752,7 +1833,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1760,7 +1841,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1768,7 +1849,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1776,7 +1857,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1784,7 +1865,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1792,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1800,7 +1881,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1808,7 +1889,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1816,7 +1897,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1830,7 +1911,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1859,18 +1940,18 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1890,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1898,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1906,7 +1987,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1914,7 +1995,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1922,7 +2003,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1930,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1938,7 +2019,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1946,7 +2027,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1954,7 +2035,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1962,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1970,7 +2051,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1978,7 +2059,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +2067,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1994,7 +2075,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2083,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2091,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2018,7 +2099,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2026,43 +2107,43 @@
         <v>24</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52AF7FE-EFA2-4D42-876D-5AC744ED69CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7923C7-54A6-4AB0-A7E3-7119758AB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="54">
   <si>
     <t>Spieler</t>
   </si>
@@ -733,7 +733,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D23" totalsRowShown="0">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Spieler"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Priorität 1"/>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="23">
         <v>6</v>
@@ -1000,10 +1000,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="23">
+        <v>5</v>
+      </c>
+      <c r="G2" s="25">
         <v>7</v>
-      </c>
-      <c r="G2" s="25">
-        <v>6</v>
       </c>
       <c r="H2" s="26">
         <v>5</v>
@@ -1069,22 +1069,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="25">
+        <v>5</v>
+      </c>
+      <c r="G5" s="28">
         <v>6</v>
       </c>
-      <c r="G5" s="28">
-        <v>8</v>
-      </c>
       <c r="H5" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1101,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="28">
         <v>8</v>
@@ -1127,10 +1127,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="23">
         <v>7</v>
@@ -1150,7 +1150,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="28">
         <v>8</v>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="29">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="24">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" s="29">
         <v>2</v>
@@ -1499,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1766,13 +1766,35 @@
       </c>
       <c r="D21" s="11"/>
     </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B5:D21" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B5:D23" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Torwart,Abwehr,Mittelfeld,Sturm,Spielmacher"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2115,7 +2137,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2123,7 +2145,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7923C7-54A6-4AB0-A7E3-7119758AB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31977E1D-CBA0-4081-BB85-DB606B2DF255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -1639,13 +1639,13 @@
         <v>15</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31977E1D-CBA0-4081-BB85-DB606B2DF255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B95C1-10F7-4B39-ACFC-0A7D74C0A7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="54">
   <si>
     <t>Spieler</t>
   </si>
@@ -1052,7 +1052,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" s="27">
         <v>9</v>
@@ -1130,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="F7" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="23">
         <v>7</v>
@@ -1381,22 +1381,22 @@
         <v>1</v>
       </c>
       <c r="C17" s="30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="21">
         <v>1</v>
       </c>
       <c r="G17" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="30">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1407,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="30">
         <v>3</v>
@@ -1462,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="D20" s="33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="31">
         <v>2</v>
@@ -1787,6 +1787,9 @@
       <c r="C23" t="s">
         <v>2</v>
       </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B95C1-10F7-4B39-ACFC-0A7D74C0A7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE678BCE-8D92-4209-80BD-99983177AF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -952,6 +952,7 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
@@ -1176,13 +1177,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="24">
         <v>4</v>
@@ -1465,7 +1466,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="34">
         <v>1</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE678BCE-8D92-4209-80BD-99983177AF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C64F2D-E444-450E-8B6D-6D24117C60A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="54">
   <si>
     <t>Spieler</t>
   </si>
@@ -1053,13 +1053,13 @@
         <v>6</v>
       </c>
       <c r="F4" s="25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="27">
         <v>9</v>
       </c>
       <c r="H4" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1160,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="23">
         <v>7</v>
@@ -1200,7 +1200,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="29">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1440,7 +1440,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" s="34">
         <v>1</v>
@@ -1466,7 +1466,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" s="34">
         <v>1</v>
@@ -1777,6 +1777,9 @@
       <c r="C22" t="s">
         <v>2</v>
       </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C64F2D-E444-450E-8B6D-6D24117C60A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BA01C1-727E-47F8-BA4E-E339B69947DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -1111,7 +1111,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
